--- a/data/Ontologies_forRepo.xlsx
+++ b/data/Ontologies_forRepo.xlsx
@@ -1794,12 +1794,12 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>nd19306e7a4224ab7b4a3e10a0f8f009eb1</t>
+          <t>n08e00a20db2e46b1a84fef015f37b665b1</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>['nd19306e7a4224ab7b4a3e10a0f8f009eb1']</t>
+          <t>['n08e00a20db2e46b1a84fef015f37b665b1']</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr"/>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>nc6f049b2c23443a18739dc1e0fdfbaceb1</t>
+          <t>n699c7b3c48824919b81a03cd5848cb64b1</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>['nc6f049b2c23443a18739dc1e0fdfbaceb1']</t>
+          <t>['n699c7b3c48824919b81a03cd5848cb64b1']</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr"/>
@@ -3247,12 +3247,12 @@
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>nd1e355ce2bcc497390a5de8def6190dcb1</t>
+          <t>n11b4b55e412a4745a4d66d81a20243f3b1</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>['nd1e355ce2bcc497390a5de8def6190dcb1']</t>
+          <t>['n11b4b55e412a4745a4d66d81a20243f3b1']</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr"/>
@@ -4558,12 +4558,12 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>bcfowl, building, contax, cto, dor, dot, dtc, eco, facility, hbpo, icdd2ams, ioc, unocs, xemo, bimxel</t>
+          <t>bcfowl, building, contax, cto, dor, dot, dtc, eco, facility, hbpo, icdd2ams, ioc, unocs, xemo, bimxel, bcore, bcorezones</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>bcfowl, building, contax, cto, dor, dot, dtc, eco, facility, hbpo, icdd2ams, ioc, unocs, xemo, bimxel</t>
+          <t>bcfowl, building, contax, cto, dor, dot, dtc, eco, facility, hbpo, icdd2ams, ioc, unocs, xemo, bimxel, bcore, bcorezones</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
@@ -4879,12 +4879,12 @@
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>n6ede6c6952d74765b87915088937a49fb8, n6ede6c6952d74765b87915088937a49fb9, n6ede6c6952d74765b87915088937a49fb10, n6ede6c6952d74765b87915088937a49fb11</t>
+          <t>nf67f55ba17394f1da203856eff6a1113b8, nf67f55ba17394f1da203856eff6a1113b9, nf67f55ba17394f1da203856eff6a1113b10, nf67f55ba17394f1da203856eff6a1113b11</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>['n6ede6c6952d74765b87915088937a49fb8', 'n6ede6c6952d74765b87915088937a49fb9', 'n6ede6c6952d74765b87915088937a49fb10', 'n6ede6c6952d74765b87915088937a49fb11']</t>
+          <t>['nf67f55ba17394f1da203856eff6a1113b8', 'nf67f55ba17394f1da203856eff6a1113b9', 'nf67f55ba17394f1da203856eff6a1113b10', 'nf67f55ba17394f1da203856eff6a1113b11']</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr"/>
@@ -5147,22 +5147,22 @@
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>n2f19e401e7014f6a8421084ec8d9999db7274</t>
+          <t>n948483d4dd08451b82b60e8883f519e0b7274</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>['n2f19e401e7014f6a8421084ec8d9999db7274']</t>
+          <t>['n948483d4dd08451b82b60e8883f519e0b7274']</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>n2f19e401e7014f6a8421084ec8d9999db7276</t>
+          <t>n948483d4dd08451b82b60e8883f519e0b7276</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>n2f19e401e7014f6a8421084ec8d9999db7276</t>
+          <t>n948483d4dd08451b82b60e8883f519e0b7276</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>bedo</t>
+          <t>bcore, bcoremedia, bcorecomp, bedo</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>bedo</t>
+          <t>bcore, bcoremedia, bcorecomp, bedo</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
@@ -5409,12 +5409,12 @@
       <c r="BM20" t="inlineStr"/>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>nf52493ed3b3943df87e698db3be3846ab1, nf52493ed3b3943df87e698db3be3846ab2</t>
+          <t>nb1b7ee0befb64bf4869fa172ee36d7d2b1, nb1b7ee0befb64bf4869fa172ee36d7d2b2</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>['nf52493ed3b3943df87e698db3be3846ab1', 'nf52493ed3b3943df87e698db3be3846ab2']</t>
+          <t>['nb1b7ee0befb64bf4869fa172ee36d7d2b1', 'nb1b7ee0befb64bf4869fa172ee36d7d2b2']</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr"/>
@@ -6123,12 +6123,12 @@
       <c r="BM23" t="inlineStr"/>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>ne619ec86c2f944c89cc63727dfcdbd37b1</t>
+          <t>n000166d343a04567b2b6b3752798d894b1</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>['ne619ec86c2f944c89cc63727dfcdbd37b1']</t>
+          <t>['n000166d343a04567b2b6b3752798d894b1']</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr"/>
@@ -6795,12 +6795,12 @@
       <c r="BM26" t="inlineStr"/>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>n50498cb26961412daa958da05531b64bb3, n50498cb26961412daa958da05531b64bb4</t>
+          <t>nfce99b8e154449d1a58e9e664acea627b3, nfce99b8e154449d1a58e9e664acea627b4</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>['n50498cb26961412daa958da05531b64bb3', 'n50498cb26961412daa958da05531b64bb4']</t>
+          <t>['nfce99b8e154449d1a58e9e664acea627b3', 'nfce99b8e154449d1a58e9e664acea627b4']</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr"/>
@@ -7253,12 +7253,12 @@
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>na8e269c577d542908801cfb1ed4a3abab1</t>
+          <t>n9a88028ab95d4173a157462bca4bfa02b1</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>['na8e269c577d542908801cfb1ed4a3abab1']</t>
+          <t>['n9a88028ab95d4173a157462bca4bfa02b1']</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr"/>
@@ -7537,12 +7537,12 @@
       <c r="BM29" t="inlineStr"/>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>n453f48f8a0cf48658d967a1a2b0dfd56b3, n453f48f8a0cf48658d967a1a2b0dfd56b4</t>
+          <t>n9aae24b156774b0d80f381a29f424611b3, n9aae24b156774b0d80f381a29f424611b4</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>['n453f48f8a0cf48658d967a1a2b0dfd56b3', 'n453f48f8a0cf48658d967a1a2b0dfd56b4']</t>
+          <t>['n9aae24b156774b0d80f381a29f424611b3', 'n9aae24b156774b0d80f381a29f424611b4']</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr"/>
@@ -7821,12 +7821,12 @@
       <c r="BM30" t="inlineStr"/>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>n4988ccb4e0d2427e8ade174094bc9fa5b3, n4988ccb4e0d2427e8ade174094bc9fa5b4</t>
+          <t>nb326674603e0428aba4a17869150382fb3, nb326674603e0428aba4a17869150382fb4</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>['n4988ccb4e0d2427e8ade174094bc9fa5b3', 'n4988ccb4e0d2427e8ade174094bc9fa5b4']</t>
+          <t>['nb326674603e0428aba4a17869150382fb3', 'nb326674603e0428aba4a17869150382fb4']</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr"/>
@@ -8098,12 +8098,12 @@
       <c r="BM31" t="inlineStr"/>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>n53412e0464a14ba289f21fa3177c98c1b1</t>
+          <t>n4621905cfd684d9e9a915b40e5bce7a9b1</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>['n53412e0464a14ba289f21fa3177c98c1b1']</t>
+          <t>['n4621905cfd684d9e9a915b40e5bce7a9b1']</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr"/>
@@ -8367,22 +8367,22 @@
       <c r="BM32" t="inlineStr"/>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>n163c5a5072a740cfa4ae80712325fef7b1</t>
+          <t>n0743fc157ba0441e8852fe43ef11839ab1</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>['n163c5a5072a740cfa4ae80712325fef7b1']</t>
+          <t>['n0743fc157ba0441e8852fe43ef11839ab1']</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>n163c5a5072a740cfa4ae80712325fef7b3</t>
+          <t>n0743fc157ba0441e8852fe43ef11839ab3</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>n163c5a5072a740cfa4ae80712325fef7b3</t>
+          <t>n0743fc157ba0441e8852fe43ef11839ab3</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13248,12 +13248,12 @@
       </c>
       <c r="BN51" t="inlineStr">
         <is>
-          <t>nc4e3aeaba8af441c8c6104b7e4cb813fb1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
+          <t>n95cd4f3c14c7445bace67a2ef6e980e2b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
         </is>
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>['nc4e3aeaba8af441c8c6104b7e4cb813fb1', 'https://www.researchgate.net/profile/Mathias_Bonduel']</t>
+          <t>['n95cd4f3c14c7445bace67a2ef6e980e2b1', 'https://www.researchgate.net/profile/Mathias_Bonduel']</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr"/>
@@ -17636,12 +17636,12 @@
       </c>
       <c r="BP69" t="inlineStr">
         <is>
-          <t>n53b1270438e140de8a3f4d95b4582e50b1</t>
+          <t>n33742bbff9d14f71b319c319078dc622b1</t>
         </is>
       </c>
       <c r="BQ69" t="inlineStr">
         <is>
-          <t>n53b1270438e140de8a3f4d95b4582e50b1</t>
+          <t>n33742bbff9d14f71b319c319078dc622b1</t>
         </is>
       </c>
       <c r="BR69" t="inlineStr">
@@ -18870,22 +18870,22 @@
       <c r="BM74" t="inlineStr"/>
       <c r="BN74" t="inlineStr">
         <is>
-          <t>n484f031b22224f5bbbdc63c6655b8d89b1</t>
+          <t>n5ddd3acffb8a47dbb19f9708c60fb1abb1</t>
         </is>
       </c>
       <c r="BO74" t="inlineStr">
         <is>
-          <t>['n484f031b22224f5bbbdc63c6655b8d89b1']</t>
+          <t>['n5ddd3acffb8a47dbb19f9708c60fb1abb1']</t>
         </is>
       </c>
       <c r="BP74" t="inlineStr">
         <is>
-          <t>n484f031b22224f5bbbdc63c6655b8d89b3</t>
+          <t>n5ddd3acffb8a47dbb19f9708c60fb1abb3</t>
         </is>
       </c>
       <c r="BQ74" t="inlineStr">
         <is>
-          <t>n484f031b22224f5bbbdc63c6655b8d89b3</t>
+          <t>n5ddd3acffb8a47dbb19f9708c60fb1abb3</t>
         </is>
       </c>
       <c r="BR74" t="inlineStr">
@@ -19382,12 +19382,12 @@
       <c r="BM76" t="inlineStr"/>
       <c r="BN76" t="inlineStr">
         <is>
-          <t>n1a1b52eb8d1e4f05973e1185f0655f84b1, n1a1b52eb8d1e4f05973e1185f0655f84b2</t>
+          <t>nd554d0ce128346aead38c2c1daec62f8b1, nd554d0ce128346aead38c2c1daec62f8b2</t>
         </is>
       </c>
       <c r="BO76" t="inlineStr">
         <is>
-          <t>['n1a1b52eb8d1e4f05973e1185f0655f84b1', 'n1a1b52eb8d1e4f05973e1185f0655f84b2']</t>
+          <t>['nd554d0ce128346aead38c2c1daec62f8b1', 'nd554d0ce128346aead38c2c1daec62f8b2']</t>
         </is>
       </c>
       <c r="BP76" t="inlineStr"/>
@@ -20459,22 +20459,22 @@
       <c r="BM80" t="inlineStr"/>
       <c r="BN80" t="inlineStr">
         <is>
-          <t>na375e7592de64c93973e5b247a09b5dcb3, na375e7592de64c93973e5b247a09b5dcb5</t>
+          <t>n526290b489ed41f099ad8560b1ea5986b3, n526290b489ed41f099ad8560b1ea5986b5</t>
         </is>
       </c>
       <c r="BO80" t="inlineStr">
         <is>
-          <t>['na375e7592de64c93973e5b247a09b5dcb3', 'na375e7592de64c93973e5b247a09b5dcb5']</t>
+          <t>['n526290b489ed41f099ad8560b1ea5986b3', 'n526290b489ed41f099ad8560b1ea5986b5']</t>
         </is>
       </c>
       <c r="BP80" t="inlineStr">
         <is>
-          <t>na375e7592de64c93973e5b247a09b5dcb7</t>
+          <t>n526290b489ed41f099ad8560b1ea5986b7</t>
         </is>
       </c>
       <c r="BQ80" t="inlineStr">
         <is>
-          <t>na375e7592de64c93973e5b247a09b5dcb7</t>
+          <t>n526290b489ed41f099ad8560b1ea5986b7</t>
         </is>
       </c>
       <c r="BR80" t="inlineStr">
@@ -21408,22 +21408,22 @@
       <c r="BM84" t="inlineStr"/>
       <c r="BN84" t="inlineStr">
         <is>
-          <t>n9043f378067d4d4fabe919d3bb370712b3, n9043f378067d4d4fabe919d3bb370712b5</t>
+          <t>n20fcca12ebc74ec4981be86babf19874b3, n20fcca12ebc74ec4981be86babf19874b5</t>
         </is>
       </c>
       <c r="BO84" t="inlineStr">
         <is>
-          <t>['n9043f378067d4d4fabe919d3bb370712b3', 'n9043f378067d4d4fabe919d3bb370712b5']</t>
+          <t>['n20fcca12ebc74ec4981be86babf19874b3', 'n20fcca12ebc74ec4981be86babf19874b5']</t>
         </is>
       </c>
       <c r="BP84" t="inlineStr">
         <is>
-          <t>n9043f378067d4d4fabe919d3bb370712b7</t>
+          <t>n20fcca12ebc74ec4981be86babf19874b7</t>
         </is>
       </c>
       <c r="BQ84" t="inlineStr">
         <is>
-          <t>n9043f378067d4d4fabe919d3bb370712b7</t>
+          <t>n20fcca12ebc74ec4981be86babf19874b7</t>
         </is>
       </c>
       <c r="BR84" t="inlineStr">
@@ -22206,12 +22206,12 @@
       </c>
       <c r="BN87" t="inlineStr">
         <is>
-          <t>n8dce8a0711834901be47a90eeedb8651b1</t>
+          <t>nd7a03ab99f6048a6ac7730bee952efa1b1</t>
         </is>
       </c>
       <c r="BO87" t="inlineStr">
         <is>
-          <t>['n8dce8a0711834901be47a90eeedb8651b1']</t>
+          <t>['nd7a03ab99f6048a6ac7730bee952efa1b1']</t>
         </is>
       </c>
       <c r="BP87" t="inlineStr"/>
@@ -24972,12 +24972,12 @@
       <c r="BM99" t="inlineStr"/>
       <c r="BN99" t="inlineStr">
         <is>
-          <t>n451e932941e846538e88adcce8e5406ab1, n451e932941e846538e88adcce8e5406ab2</t>
+          <t>n2118551a185e4ddc8ab06baca74ab0dcb1, n2118551a185e4ddc8ab06baca74ab0dcb2</t>
         </is>
       </c>
       <c r="BO99" t="inlineStr">
         <is>
-          <t>['n451e932941e846538e88adcce8e5406ab1', 'n451e932941e846538e88adcce8e5406ab2']</t>
+          <t>['n2118551a185e4ddc8ab06baca74ab0dcb1', 'n2118551a185e4ddc8ab06baca74ab0dcb2']</t>
         </is>
       </c>
       <c r="BP99" t="inlineStr"/>
@@ -26359,8 +26359,16 @@
       <c r="AP105" t="b">
         <v>1</v>
       </c>
-      <c r="AQ105" t="inlineStr"/>
-      <c r="AR105" t="inlineStr"/>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>bcore</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>bcore</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0.64</v>
@@ -33668,12 +33676,12 @@
       <c r="BM132" t="inlineStr"/>
       <c r="BN132" t="inlineStr">
         <is>
-          <t>n974c0cb2c33643e2a0d58187e9f39ccdb1</t>
+          <t>nc7a558cfbf2a4eb98d4e25c47c1a4cffb1</t>
         </is>
       </c>
       <c r="BO132" t="inlineStr">
         <is>
-          <t>['n974c0cb2c33643e2a0d58187e9f39ccdb1']</t>
+          <t>['nc7a558cfbf2a4eb98d4e25c47c1a4cffb1']</t>
         </is>
       </c>
       <c r="BP132" t="inlineStr"/>
@@ -33938,12 +33946,12 @@
       <c r="BM133" t="inlineStr"/>
       <c r="BN133" t="inlineStr">
         <is>
-          <t>nec1dc9163d9f4804b11db9e845d92c58b1</t>
+          <t>nc0ac74a92d0f4a30a35d7331dd0242dcb1</t>
         </is>
       </c>
       <c r="BO133" t="inlineStr">
         <is>
-          <t>['nec1dc9163d9f4804b11db9e845d92c58b1']</t>
+          <t>['nc0ac74a92d0f4a30a35d7331dd0242dcb1']</t>
         </is>
       </c>
       <c r="BP133" t="inlineStr"/>
@@ -34467,22 +34475,22 @@
       </c>
       <c r="BN135" t="inlineStr">
         <is>
-          <t>n9d1446a2f1e04861b4771178230d42c0b1, n9d1446a2f1e04861b4771178230d42c0b3, n9d1446a2f1e04861b4771178230d42c0b5, n9d1446a2f1e04861b4771178230d42c0b7</t>
+          <t>n483805cb276445399ed40974aae1ed40b1, n483805cb276445399ed40974aae1ed40b3, n483805cb276445399ed40974aae1ed40b5, n483805cb276445399ed40974aae1ed40b7</t>
         </is>
       </c>
       <c r="BO135" t="inlineStr">
         <is>
-          <t>['n9d1446a2f1e04861b4771178230d42c0b1', 'n9d1446a2f1e04861b4771178230d42c0b3', 'n9d1446a2f1e04861b4771178230d42c0b5', 'n9d1446a2f1e04861b4771178230d42c0b7']</t>
+          <t>['n483805cb276445399ed40974aae1ed40b1', 'n483805cb276445399ed40974aae1ed40b3', 'n483805cb276445399ed40974aae1ed40b5', 'n483805cb276445399ed40974aae1ed40b7']</t>
         </is>
       </c>
       <c r="BP135" t="inlineStr">
         <is>
-          <t>n9d1446a2f1e04861b4771178230d42c0b9</t>
+          <t>n483805cb276445399ed40974aae1ed40b9</t>
         </is>
       </c>
       <c r="BQ135" t="inlineStr">
         <is>
-          <t>n9d1446a2f1e04861b4771178230d42c0b9</t>
+          <t>n483805cb276445399ed40974aae1ed40b9</t>
         </is>
       </c>
       <c r="BR135" t="inlineStr">
@@ -37381,22 +37389,20 @@
       <c r="B149" t="b">
         <v>1</v>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>at line 108 of &lt;&gt;:
-Bad syntax (Prefix ":" not bound) at ^ in:
-"...b'#################\n\n###  https://w3id.org/bcore#bridgesRoute\n'^b':bridgesRoute rdf:type owl:ObjectProperty ;\n              rd'..."</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Bcore</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>bcore</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>bcore</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bcore</t>
+          <t>bcore</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -37404,10 +37410,14 @@
           <t>Bridge Core Ontology</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Bridge Core Ontology</t>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -37415,7 +37425,11 @@
           <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD).</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Core ontology for the representation of bridges.</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD).</t>
@@ -37424,21 +37438,35 @@
       <c r="M149" t="n">
         <v>2025</v>
       </c>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="n">
-        <v>2025</v>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -37446,7 +37474,11 @@
           <t>0.1.1</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr"/>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>0.1.1</t>
+        </is>
+      </c>
       <c r="W149" t="inlineStr">
         <is>
           <t>0.1.1</t>
@@ -37457,29 +37489,51 @@
           <t>reloc, brot, brcomp, bot, bmat, infraspatialot</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr"/>
-      <c r="Z149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>brot, bot, reloc, infraspatialot, bcoremedia</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>brot, bot, reloc, infraspatialot, bcoremedia</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>vann, foaf, schema, bibo</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr"/>
-      <c r="AC149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema, bmat, brcomp</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema, bmat, brcomp</t>
+        </is>
+      </c>
       <c r="AD149" t="inlineStr"/>
       <c r="AE149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
       <c r="AI149" t="inlineStr"/>
       <c r="AJ149" t="inlineStr"/>
-      <c r="AK149" t="inlineStr"/>
-      <c r="AL149" t="inlineStr"/>
-      <c r="AM149" t="inlineStr"/>
+      <c r="AK149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>100</v>
+      </c>
       <c r="AN149" t="inlineStr"/>
       <c r="AO149" t="b">
         <v>1</v>
@@ -37491,10 +37545,10 @@
       <c r="AR149" t="inlineStr"/>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
-        <v>0.74</v>
+        <v>0.08</v>
       </c>
       <c r="AU149" t="n">
-        <v>0.74</v>
+        <v>0.08</v>
       </c>
       <c r="AV149" t="inlineStr"/>
       <c r="AW149" t="inlineStr"/>
@@ -37542,38 +37596,58 @@
       <c r="BK149" t="inlineStr"/>
       <c r="BL149" t="inlineStr"/>
       <c r="BM149" t="inlineStr"/>
-      <c r="BN149" t="inlineStr"/>
+      <c r="BN149" t="inlineStr">
+        <is>
+          <t>Johannes Reimer, Morris Florek, Tim Noack, Xiaoli Song</t>
+        </is>
+      </c>
       <c r="BO149" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Johannes Reimer', 'Morris Florek', 'Tim Noack', 'Xiaoli Song']</t>
         </is>
       </c>
       <c r="BP149" t="inlineStr"/>
       <c r="BQ149" t="inlineStr"/>
-      <c r="BR149" t="inlineStr"/>
-      <c r="BS149" t="inlineStr"/>
-      <c r="BT149" t="inlineStr"/>
-      <c r="BU149" t="inlineStr"/>
-      <c r="BV149" t="inlineStr"/>
-      <c r="BW149" t="inlineStr"/>
-      <c r="BX149" t="inlineStr"/>
+      <c r="BR149" t="inlineStr">
+        <is>
+          <t>{brot: https://w3id.org/brot#}, {bot: https://w3id.org/bot#}, {reloc: https://w3id.org/reloc#}, {infraspatialot: https://dtc-ontology.cms.ed.tum.de/infraspatialot#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {bibo: http://purl.org/ontology/bibo/}, {vann: http://purl.org/vocab/vann/}, {foaf: http://xmlns.com/foaf/0.1/}, {schema: https://schema.org/}, {bcoremedia: https://w3id.org/bcore/media#}, {bmat: https://w3id.org/bmat#}, {brcomp: https://w3id.org/brcomp#}</t>
+        </is>
+      </c>
+      <c r="BS149" t="n">
+        <v>18</v>
+      </c>
+      <c r="BT149" t="n">
+        <v>18</v>
+      </c>
+      <c r="BU149" t="n">
+        <v>31</v>
+      </c>
+      <c r="BV149" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW149" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX149" t="n">
+        <v>30</v>
+      </c>
       <c r="BY149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CC149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -37585,22 +37659,20 @@
       <c r="B150" t="b">
         <v>1</v>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>at line 108 of &lt;&gt;:
-Bad syntax (Prefix ":" not bound) at ^ in:
-"...b'#################\n\n###  https://w3id.org/bcore#bridgesRoute\n'^b':bridgesRoute rdf:type owl:ObjectProperty ;\n              rd'..."</t>
-        </is>
-      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>bcore</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>bcoremedia</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>bcoremedia</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>bcore</t>
+          <t>bcoremedia</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -37608,10 +37680,14 @@
           <t>Bridge Core Ontology – Media Extension</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Media Extension</t>
+        </is>
+      </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Bridge Core Ontology – Media Extension</t>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Media Extension</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -37621,7 +37697,11 @@
 BCoreMedia builds directly on BCore’s top‑level structure, ensuring that every media item can be consistently linked to the bridge, its components, its materials, or its spatial context. It integrates seamlessly with component, material, infrastructure, and zone modules to enable rich, multi‑domain documentation workflows.</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Extension ontology for the representation of bridge-related media. Designed to work in conjunction with the BCore ontology but to also allow for external use.</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>The BCoreMedia Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing bridge‑related media and documentation.
@@ -37632,21 +37712,35 @@
       <c r="M150" t="n">
         <v>2025</v>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="n">
-        <v>2025</v>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
+        </is>
+      </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -37654,7 +37748,11 @@
           <t>0.1.1</t>
         </is>
       </c>
-      <c r="V150" t="inlineStr"/>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>0.1.1</t>
+        </is>
+      </c>
       <c r="W150" t="inlineStr">
         <is>
           <t>0.1.1</t>
@@ -37665,44 +37763,74 @@
           <t>bcore, brot</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr"/>
-      <c r="Z150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>vann, foaf, schema, bibo</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr"/>
-      <c r="AC150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
       <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
       <c r="AI150" t="inlineStr"/>
       <c r="AJ150" t="inlineStr"/>
-      <c r="AK150" t="inlineStr"/>
-      <c r="AL150" t="inlineStr"/>
-      <c r="AM150" t="inlineStr"/>
+      <c r="AK150" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL150" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>100</v>
+      </c>
       <c r="AN150" t="inlineStr"/>
       <c r="AO150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP150" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ150" t="inlineStr"/>
-      <c r="AR150" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>bcore</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>bcore</t>
+        </is>
+      </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>0.7</v>
+        <v>0.08</v>
       </c>
       <c r="AU150" t="n">
-        <v>0.7</v>
+        <v>0.08</v>
       </c>
       <c r="AV150" t="inlineStr"/>
       <c r="AW150" t="inlineStr"/>
@@ -37742,38 +37870,58 @@
       <c r="BK150" t="inlineStr"/>
       <c r="BL150" t="inlineStr"/>
       <c r="BM150" t="inlineStr"/>
-      <c r="BN150" t="inlineStr"/>
+      <c r="BN150" t="inlineStr">
+        <is>
+          <t>Johannes Reimer, Morris Florek, Tim Noack, Xiaoli Song</t>
+        </is>
+      </c>
       <c r="BO150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Johannes Reimer', 'Morris Florek', 'Tim Noack', 'Xiaoli Song']</t>
         </is>
       </c>
       <c r="BP150" t="inlineStr"/>
       <c r="BQ150" t="inlineStr"/>
-      <c r="BR150" t="inlineStr"/>
-      <c r="BS150" t="inlineStr"/>
-      <c r="BT150" t="inlineStr"/>
-      <c r="BU150" t="inlineStr"/>
-      <c r="BV150" t="inlineStr"/>
-      <c r="BW150" t="inlineStr"/>
-      <c r="BX150" t="inlineStr"/>
+      <c r="BR150" t="inlineStr">
+        <is>
+          <t>{brot: https://w3id.org/brot#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {bibo: http://purl.org/ontology/bibo/}, {vann: http://purl.org/vocab/vann/}, {foaf: http://xmlns.com/foaf/0.1/}, {schema: https://schema.org/}</t>
+        </is>
+      </c>
+      <c r="BS150" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT150" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX150" t="n">
+        <v>2</v>
+      </c>
       <c r="BY150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA150" t="b">
         <v>0</v>
       </c>
       <c r="CB150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CC150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -37785,19 +37933,17 @@
       <c r="B151" t="b">
         <v>1</v>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>at line 103 of &lt;&gt;:
-Bad syntax (Prefix ":" not bound) at ^ in:
-"...b'################\n\n###  https://w3id.org/bcore/zones#BuiltUpA'^b'rea\n:BuiltUpArea rdf:type owl:Class ;\n             rdfs:subC'..."</t>
-        </is>
-      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>bcorezones</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>bcorezones</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>bcorezones</t>
@@ -37808,10 +37954,14 @@
           <t>Bridge Core Ontology – Zones Extension</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Zones Extension</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Bridge Core Ontology – Zones Extension</t>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Zones Extension</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -37821,7 +37971,11 @@
 BCoreZones builds directly on BCore’s top‑level structure, ensuring that every spatial zone can be consistently linked to the bridge or its components. It integrates seamlessly with component, material, infrastructure, and media modules to support comprehensive, multi‑domain bridge modeling.</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Extension ontology for the representation of bridge-related zones. Designed to work in conjunction with the BCore ontology but to also allow for external use.</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>The BCoreZones Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing spatial zones and environmental context around a bridge.
@@ -37832,21 +37986,35 @@
       <c r="M151" t="n">
         <v>2025</v>
       </c>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="n">
-        <v>2025</v>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
+        </is>
+      </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -37854,7 +38022,11 @@
           <t>0.1.1</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr"/>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>0.1.1</t>
+        </is>
+      </c>
       <c r="W151" t="inlineStr">
         <is>
           <t>0.1.1</t>
@@ -37865,29 +38037,51 @@
           <t>bot</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr"/>
-      <c r="Z151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>bot</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>bot</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>vann, foaf, schema, bibo</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr"/>
-      <c r="AC151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
       <c r="AD151" t="inlineStr"/>
       <c r="AE151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
       <c r="AI151" t="inlineStr"/>
       <c r="AJ151" t="inlineStr"/>
-      <c r="AK151" t="inlineStr"/>
-      <c r="AL151" t="inlineStr"/>
-      <c r="AM151" t="inlineStr"/>
+      <c r="AK151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>100</v>
+      </c>
       <c r="AN151" t="inlineStr"/>
       <c r="AO151" t="b">
         <v>1</v>
@@ -37958,38 +38152,58 @@
           <t>Geometry</t>
         </is>
       </c>
-      <c r="BN151" t="inlineStr"/>
+      <c r="BN151" t="inlineStr">
+        <is>
+          <t>Johannes Reimer, Morris Florek, Tim Noack, Xiaoli Song</t>
+        </is>
+      </c>
       <c r="BO151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Johannes Reimer', 'Morris Florek', 'Tim Noack', 'Xiaoli Song']</t>
         </is>
       </c>
       <c r="BP151" t="inlineStr"/>
       <c r="BQ151" t="inlineStr"/>
-      <c r="BR151" t="inlineStr"/>
-      <c r="BS151" t="inlineStr"/>
-      <c r="BT151" t="inlineStr"/>
-      <c r="BU151" t="inlineStr"/>
-      <c r="BV151" t="inlineStr"/>
-      <c r="BW151" t="inlineStr"/>
-      <c r="BX151" t="inlineStr"/>
+      <c r="BR151" t="inlineStr">
+        <is>
+          <t>{bot: https://w3id.org/bot#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {bibo: http://purl.org/ontology/bibo/}, {vann: http://purl.org/vocab/vann/}, {foaf: http://xmlns.com/foaf/0.1/}, {schema: https://schema.org/}</t>
+        </is>
+      </c>
+      <c r="BS151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>0</v>
+      </c>
       <c r="BY151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CC151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -38001,19 +38215,17 @@
       <c r="B152" t="b">
         <v>1</v>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>at line 105 of &lt;&gt;:
-Bad syntax (Prefix ":" not bound) at ^ in:
-"...b'#########\n\n###  https://w3id.org/bcore/infra#FootCycleRouteT'^b'ype\n:FootCycleRouteType rdf:type owl:DatatypeProperty ,\n    '..."</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>bcoreinfra</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>bcoreinfra</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>bcoreinfra</t>
@@ -38024,10 +38236,14 @@
           <t>Bridge Core Ontology – Infrastructure Extension</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Infrastructure Extension</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Bridge Core Ontology – Infrastructure Extension</t>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Infrastructure Extension</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -38036,7 +38252,11 @@
 It models roads, railways, waterways, and other contextual infrastructure elements that interact with or influence the bridge. BCoreInfra builds directly on BCore’s top‑level structure, ensuring that every infrastructure element can be consistently linked to the bridge it serves or affects. It integrates seamlessly with component, material, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling.</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Extension ontology for the representation of bridge-related infrastructure. Designed to work in conjunction with the BCore ontology but to also allow for external use.</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>The BCoreInfra Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing bridge-related infrastructure.
@@ -38046,21 +38266,35 @@
       <c r="M152" t="n">
         <v>2025</v>
       </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="n">
-        <v>2025</v>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
-      <c r="S152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
+        </is>
+      </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -38068,7 +38302,11 @@
           <t>0.1.1</t>
         </is>
       </c>
-      <c r="V152" t="inlineStr"/>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>0.1.1</t>
+        </is>
+      </c>
       <c r="W152" t="inlineStr">
         <is>
           <t>0.1.1</t>
@@ -38086,22 +38324,36 @@
           <t>vann, foaf, schema, bibo</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr"/>
-      <c r="AC152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
       <c r="AI152" t="inlineStr"/>
       <c r="AJ152" t="inlineStr"/>
-      <c r="AK152" t="inlineStr"/>
-      <c r="AL152" t="inlineStr"/>
-      <c r="AM152" t="inlineStr"/>
+      <c r="AK152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>100</v>
+      </c>
       <c r="AN152" t="inlineStr"/>
       <c r="AO152" t="b">
         <v>1</v>
@@ -38164,23 +38416,43 @@
       <c r="BK152" t="inlineStr"/>
       <c r="BL152" t="inlineStr"/>
       <c r="BM152" t="inlineStr"/>
-      <c r="BN152" t="inlineStr"/>
+      <c r="BN152" t="inlineStr">
+        <is>
+          <t>Johannes Reimer, Morris Florek, Tim Noack, Xiaoli Song</t>
+        </is>
+      </c>
       <c r="BO152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Johannes Reimer', 'Morris Florek', 'Tim Noack', 'Xiaoli Song']</t>
         </is>
       </c>
       <c r="BP152" t="inlineStr"/>
       <c r="BQ152" t="inlineStr"/>
-      <c r="BR152" t="inlineStr"/>
-      <c r="BS152" t="inlineStr"/>
-      <c r="BT152" t="inlineStr"/>
-      <c r="BU152" t="inlineStr"/>
-      <c r="BV152" t="inlineStr"/>
-      <c r="BW152" t="inlineStr"/>
-      <c r="BX152" t="inlineStr"/>
+      <c r="BR152" t="inlineStr">
+        <is>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {bibo: http://purl.org/ontology/bibo/}, {vann: http://purl.org/vocab/vann/}, {foaf: http://xmlns.com/foaf/0.1/}, {schema: https://schema.org/}</t>
+        </is>
+      </c>
+      <c r="BS152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX152" t="n">
+        <v>0</v>
+      </c>
       <c r="BY152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ152" t="b">
         <v>0</v>
@@ -38189,13 +38461,13 @@
         <v>0</v>
       </c>
       <c r="CB152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -38207,19 +38479,17 @@
       <c r="B153" t="b">
         <v>1</v>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>at line 106 of &lt;&gt;:
-Bad syntax (Prefix ":" not bound) at ^ in:
-"...b'################\n\n###  https://w3id.org/bcore/mat#isComposit'^b'eOf\n:isCompositeOf rdf:type owl:ObjectProperty ;\n           '..."</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>bcoremat</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>bcoremat</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>bcoremat</t>
@@ -38230,10 +38500,14 @@
           <t>Bridge Core Ontology – Material Extension</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Material Extension</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Bridge Core Ontology – Material Extension</t>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Material Extension</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -38241,7 +38515,11 @@
           <t>The BCoreMat Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing materials used in bridge construction. It models concrete, steel, composites, coatings, and other material types, along with their properties and classifications. This enables consistent, semantically rich descriptions of what bridges and their components are made of. BCoreMat builds directly on BCore’s top‑level structure, ensuring that every material can be consistently linked to the bridge or its components. It integrates seamlessly with component, infrastructure, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling. #### BCore Ontology Suite: | Module | Purpose | |--------|---------| | BCore | Core identity, top‑level bridge concepts, and shared linking structure. | | BCoreComp | Structural and functional bridge components. | | BCoreMat | Materials used in bridge construction. | | BCoreInfra | Bridge-related transport and utility infrastructure. | | BCoreZones | Spatial zones, geometric context, and environmental regions. | | BCoreMedia | Media files, documentation, and digital assets. | #### About BCoreMat: BCoreMat provides a structured, extensible model for representing the various materials used in bridge construction. Main focus: - Material types such as concrete, steel, composites, and coatings - Material properties relevant for structural and durability assessment - Clear relationships between materials and bridge components - Consistent integration with BCore’s core identity and structure - Interoperability across all BCore modules → Thus, it is the right choice when you need to describe what a bridge is made of and how material information supports analysis, inspection, and lifecycle management.</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Extension ontology for the representation of bridge building materials. Designed to work in conjunction with the BCore ontology but to also allow for external use.</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>The BCoreMat Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing materials used in bridge construction. It models concrete, steel, composites, coatings, and other material types, along with their properties and classifications. This enables consistent, semantically rich descriptions of what bridges and their components are made of. BCoreMat builds directly on BCore’s top‑level structure, ensuring that every material can be consistently linked to the bridge or its components. It integrates seamlessly with component, infrastructure, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling. #### BCore Ontology Suite: | Module | Purpose | |--------|---------| | BCore | Core identity, top‑level bridge concepts, and shared linking structure. | | BCoreComp | Structural and functional bridge components. | | BCoreMat | Materials used in bridge construction. | | BCoreInfra | Bridge-related transport and utility infrastructure. | | BCoreZones | Spatial zones, geometric context, and environmental regions. | | BCoreMedia | Media files, documentation, and digital assets. | #### About BCoreMat: BCoreMat provides a structured, extensible model for representing the various materials used in bridge construction. Main focus: - Material types such as concrete, steel, composites, and coatings - Material properties relevant for structural and durability assessment - Clear relationships between materials and bridge components - Consistent integration with BCore’s core identity and structure - Interoperability across all BCore modules → Thus, it is the right choice when you need to describe what a bridge is made of and how material information supports analysis, inspection, and lifecycle management.</t>
@@ -38250,21 +38528,35 @@
       <c r="M153" t="n">
         <v>2025</v>
       </c>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="n">
-        <v>2025</v>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
-      <c r="S153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
+        </is>
+      </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -38272,7 +38564,11 @@
           <t>0.1.1</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr"/>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>0.1.1</t>
+        </is>
+      </c>
       <c r="W153" t="inlineStr">
         <is>
           <t>0.1.1</t>
@@ -38290,22 +38586,36 @@
           <t>vann, foaf, schema, bibo</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr"/>
-      <c r="AC153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>bmat, dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>bmat, dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
       <c r="AD153" t="inlineStr"/>
       <c r="AE153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
       <c r="AI153" t="inlineStr"/>
       <c r="AJ153" t="inlineStr"/>
-      <c r="AK153" t="inlineStr"/>
-      <c r="AL153" t="inlineStr"/>
-      <c r="AM153" t="inlineStr"/>
+      <c r="AK153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>100</v>
+      </c>
       <c r="AN153" t="inlineStr"/>
       <c r="AO153" t="b">
         <v>1</v>
@@ -38376,23 +38686,43 @@
           <t>BE Product (Infrastructure)</t>
         </is>
       </c>
-      <c r="BN153" t="inlineStr"/>
+      <c r="BN153" t="inlineStr">
+        <is>
+          <t>Johannes Reimer, Morris Florek, Tim Noack, Xiaoli Song</t>
+        </is>
+      </c>
       <c r="BO153" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Johannes Reimer', 'Morris Florek', 'Tim Noack', 'Xiaoli Song']</t>
         </is>
       </c>
       <c r="BP153" t="inlineStr"/>
       <c r="BQ153" t="inlineStr"/>
-      <c r="BR153" t="inlineStr"/>
-      <c r="BS153" t="inlineStr"/>
-      <c r="BT153" t="inlineStr"/>
-      <c r="BU153" t="inlineStr"/>
-      <c r="BV153" t="inlineStr"/>
-      <c r="BW153" t="inlineStr"/>
-      <c r="BX153" t="inlineStr"/>
+      <c r="BR153" t="inlineStr">
+        <is>
+          <t>{bmat: https://w3id.org/bmat#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {bibo: http://purl.org/ontology/bibo/}, {vann: http://purl.org/vocab/vann/}, {foaf: http://xmlns.com/foaf/0.1/}, {schema: https://schema.org/}</t>
+        </is>
+      </c>
+      <c r="BS153" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT153" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX153" t="n">
+        <v>1</v>
+      </c>
       <c r="BY153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ153" t="b">
         <v>0</v>
@@ -38401,13 +38731,13 @@
         <v>0</v>
       </c>
       <c r="CB153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -38419,19 +38749,17 @@
       <c r="B154" t="b">
         <v>1</v>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>at line 111 of &lt;&gt;:
-Bad syntax (Prefix ":" not bound) at ^ in:
-"...b'############\n\n###  https://w3id.org/bcore/comp#beginsAtLocat'^b'ion\n:beginsAtLocation rdf:type owl:ObjectProperty ,\n        '..."</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>bcorecomp</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>bcorecomp</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>bcorecomp</t>
@@ -38442,10 +38770,14 @@
           <t>Bridge Core Ontology – Components Extension</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Components Extension</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Bridge Core Ontology – Components Extension</t>
+          <t>Bridge Core Ontology for Institute of Concrete Structures, Dresden University of Technology – Components Extension</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -38453,7 +38785,11 @@
           <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD). This ontology contains the corresponding components extension.</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Extension ontology for the representation of bridge components. Designed to work in conjunction with the BCore ontology but to also allow for external use.</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD). This ontology contains the corresponding components extension.</t>
@@ -38462,21 +38798,35 @@
       <c r="M154" t="n">
         <v>2025</v>
       </c>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="n">
-        <v>2025</v>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
+        </is>
+      </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>https://creativecommons.org/licenses/by/4.0/deed.en</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -38484,7 +38834,11 @@
           <t>0.1.1</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr"/>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>0.1.1</t>
+        </is>
+      </c>
       <c r="W154" t="inlineStr">
         <is>
           <t>0.1.1</t>
@@ -38495,29 +38849,51 @@
           <t>brot, brcomp, infraspatialot</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr"/>
-      <c r="Z154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>brot, infraspatialot</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>brot, infraspatialot</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>vann, foaf, schema, bibo</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr"/>
-      <c r="AC154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>brcomp, dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>brcomp, dc, dcterms, bibo, vann, foaf, schema</t>
+        </is>
+      </c>
       <c r="AD154" t="inlineStr"/>
       <c r="AE154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
       <c r="AI154" t="inlineStr"/>
       <c r="AJ154" t="inlineStr"/>
-      <c r="AK154" t="inlineStr"/>
-      <c r="AL154" t="inlineStr"/>
-      <c r="AM154" t="inlineStr"/>
+      <c r="AK154" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL154" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>100</v>
+      </c>
       <c r="AN154" t="inlineStr"/>
       <c r="AO154" t="b">
         <v>1</v>
@@ -38588,38 +38964,58 @@
           <t>Facilities Management</t>
         </is>
       </c>
-      <c r="BN154" t="inlineStr"/>
+      <c r="BN154" t="inlineStr">
+        <is>
+          <t>Johannes Reimer, Morris Florek, Tim Noack, Xiaoli Song</t>
+        </is>
+      </c>
       <c r="BO154" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Johannes Reimer', 'Morris Florek', 'Tim Noack', 'Xiaoli Song']</t>
         </is>
       </c>
       <c r="BP154" t="inlineStr"/>
       <c r="BQ154" t="inlineStr"/>
-      <c r="BR154" t="inlineStr"/>
-      <c r="BS154" t="inlineStr"/>
-      <c r="BT154" t="inlineStr"/>
-      <c r="BU154" t="inlineStr"/>
-      <c r="BV154" t="inlineStr"/>
-      <c r="BW154" t="inlineStr"/>
-      <c r="BX154" t="inlineStr"/>
+      <c r="BR154" t="inlineStr">
+        <is>
+          <t>{brot: https://w3id.org/brot#}, {brcomp: https://w3id.org/brcomp#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {bibo: http://purl.org/ontology/bibo/}, {vann: http://purl.org/vocab/vann/}, {foaf: http://xmlns.com/foaf/0.1/}, {infraspatialot: https://dtc-ontology.cms.ed.tum.de/infraspatialot#}, {schema: https://schema.org/}</t>
+        </is>
+      </c>
+      <c r="BS154" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>36</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>8</v>
+      </c>
       <c r="BY154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA154" t="b">
         <v>0</v>
       </c>
       <c r="CB154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CC154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -39205,8 +39601,16 @@
       <c r="AP157" t="b">
         <v>1</v>
       </c>
-      <c r="AQ157" t="inlineStr"/>
-      <c r="AR157" t="inlineStr"/>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>bcore, bcorecomp</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>bcore, bcorecomp</t>
+        </is>
+      </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0.59</v>

--- a/data/Ontologies_forRepo.xlsx
+++ b/data/Ontologies_forRepo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH157"/>
+  <dimension ref="A1:CH159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,12 +1850,12 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>n051fc69bd461486ca10f9025fc99477ab1</t>
+          <t>n37add634c1ab498cb948a7fa86936747b1</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>n051fc69bd461486ca10f9025fc99477ab1</t>
+          <t>n37add634c1ab498cb948a7fa86936747b1</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr"/>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>nebf49109c8634b9d8df5721e35341f53b1</t>
+          <t>n3d9f1dd166da442da814fc23fa4b1084b1</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>nebf49109c8634b9d8df5721e35341f53b1</t>
+          <t>n3d9f1dd166da442da814fc23fa4b1084b1</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr"/>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>brot, bot, reloc, infraspatialot, bcoremedia</t>
+          <t>brot, bot, reloc, infraspatialot, bcoremedia, bmat</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>brot, bot, reloc, infraspatialot, bcoremedia</t>
+          <t>brot, bot, reloc, infraspatialot, bcoremedia, bmat</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>dc, dcterms, bibo, vann, foaf, schema, bmat, brcomp</t>
+          <t>dc, dcterms, bibo, vann, foaf, schema, brcomp</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>dc, dcterms, bibo, vann, foaf, schema, bmat, brcomp</t>
+          <t>dc, dcterms, bibo, vann, foaf, schema, brcomp</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://w3id.org/bcore/comp</t>
+          <t>https://w3id.org/bcore/comp#</t>
         </is>
       </c>
       <c r="B11" t="b">
@@ -3486,7 +3486,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://w3id.org/bcore/infra</t>
+          <t>https://w3id.org/bcore/infra#</t>
         </is>
       </c>
       <c r="B12" t="b">
@@ -3762,7 +3762,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://w3id.org/bcore/mat</t>
+          <t>https://w3id.org/bcore/mat#</t>
         </is>
       </c>
       <c r="B13" t="b">
@@ -3865,11 +3865,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>bcore</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>bcore, bmat</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>bmat</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>bmat</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>vann, foaf, schema, bibo</t>
@@ -3877,12 +3885,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>bmat, dc, dcterms, bibo, vann, foaf, schema</t>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>bmat, dc, dcterms, bibo, vann, foaf, schema</t>
+          <t>dc, dcterms, bibo, vann, foaf, schema</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -4014,13 +4022,13 @@
         <v>1</v>
       </c>
       <c r="BZ13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA13" t="b">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4044,7 +4052,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://w3id.org/bcore/media</t>
+          <t>https://w3id.org/bcore/media#</t>
         </is>
       </c>
       <c r="B14" t="b">
@@ -4218,10 +4226,10 @@
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
@@ -4330,7 +4338,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://w3id.org/bcore/zones</t>
+          <t>https://w3id.org/bcore/zones#</t>
         </is>
       </c>
       <c r="B15" t="b">
@@ -5561,12 +5569,12 @@
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>nc29cda6e1fb6476eae76fd998bccf4e6b1</t>
+          <t>ne9049731d41245fdb9604b40945f820fb1</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>nc29cda6e1fb6476eae76fd998bccf4e6b1</t>
+          <t>ne9049731d41245fdb9604b40945f820fb1</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr"/>
@@ -7537,12 +7545,12 @@
       <c r="BM27" t="inlineStr"/>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>n186cd50b1ad349888714233d7ee55eb9b8, n186cd50b1ad349888714233d7ee55eb9b9, n186cd50b1ad349888714233d7ee55eb9b10, n186cd50b1ad349888714233d7ee55eb9b11</t>
+          <t>n93b9729fe41b4116b4b844a34fd6e556b8, n93b9729fe41b4116b4b844a34fd6e556b9, n93b9729fe41b4116b4b844a34fd6e556b10, n93b9729fe41b4116b4b844a34fd6e556b11</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>n186cd50b1ad349888714233d7ee55eb9b8, n186cd50b1ad349888714233d7ee55eb9b9, n186cd50b1ad349888714233d7ee55eb9b10, n186cd50b1ad349888714233d7ee55eb9b11</t>
+          <t>n93b9729fe41b4116b4b844a34fd6e556b8, n93b9729fe41b4116b4b844a34fd6e556b9, n93b9729fe41b4116b4b844a34fd6e556b10, n93b9729fe41b4116b4b844a34fd6e556b11</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr"/>
@@ -7817,22 +7825,22 @@
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>n5d86b0eeebf648efbe7729fb2cf897a1b7274</t>
+          <t>n54ed29e592f049fa9c635904677b4703b7274</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>n5d86b0eeebf648efbe7729fb2cf897a1b7274</t>
+          <t>n54ed29e592f049fa9c635904677b4703b7274</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>n5d86b0eeebf648efbe7729fb2cf897a1b7276</t>
+          <t>n54ed29e592f049fa9c635904677b4703b7276</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>n5d86b0eeebf648efbe7729fb2cf897a1b7276</t>
+          <t>n54ed29e592f049fa9c635904677b4703b7276</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -8036,12 +8044,12 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>bcore, bcorecomp, bcoremedia, bedo</t>
+          <t>bcore, bcorecomp, bcoremedia, bedo, bmat, brcomp</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>bcore, bcorecomp, bcoremedia, bedo</t>
+          <t>bcore, bcorecomp, bcoremedia, bedo, bmat, brcomp</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
@@ -8091,12 +8099,12 @@
       <c r="BM29" t="inlineStr"/>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>n853daf604e094e68b5b4eda554efe446b1, n853daf604e094e68b5b4eda554efe446b2</t>
+          <t>nc73f03e7dd51442c9baea22cf394a7f6b1, nc73f03e7dd51442c9baea22cf394a7f6b2</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>n853daf604e094e68b5b4eda554efe446b1, n853daf604e094e68b5b4eda554efe446b2</t>
+          <t>nc73f03e7dd51442c9baea22cf394a7f6b1, nc73f03e7dd51442c9baea22cf394a7f6b2</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr"/>
@@ -8837,12 +8845,12 @@
       <c r="BM32" t="inlineStr"/>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>nd11198aa82554de5b40d2cf014d4d25fb1</t>
+          <t>n4a5b99de31cc418f8e6b771499ab9653b1</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>nd11198aa82554de5b40d2cf014d4d25fb1</t>
+          <t>n4a5b99de31cc418f8e6b771499ab9653b1</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr"/>
@@ -9537,12 +9545,12 @@
       <c r="BM35" t="inlineStr"/>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>n15827cb90fce43df8294d98f7b1a69d0b3, n15827cb90fce43df8294d98f7b1a69d0b4</t>
+          <t>n5253fd3235204cb19cc4c87c2fa4b5b3b3, n5253fd3235204cb19cc4c87c2fa4b5b3b4</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>n15827cb90fce43df8294d98f7b1a69d0b3, n15827cb90fce43df8294d98f7b1a69d0b4</t>
+          <t>n5253fd3235204cb19cc4c87c2fa4b5b3b3, n5253fd3235204cb19cc4c87c2fa4b5b3b4</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr"/>
@@ -10015,12 +10023,12 @@
       </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>nb19a3959f4b54eeaa5181b80535272c6b1</t>
+          <t>n88ed93e1111644cd99d04863357c6acbb1</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>nb19a3959f4b54eeaa5181b80535272c6b1</t>
+          <t>n88ed93e1111644cd99d04863357c6acbb1</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr"/>
@@ -10311,12 +10319,12 @@
       <c r="BM38" t="inlineStr"/>
       <c r="BN38" t="inlineStr">
         <is>
-          <t>n4f3d3308f60d48e78aa7729ed0028a2fb3, n4f3d3308f60d48e78aa7729ed0028a2fb4</t>
+          <t>nca082b3b2a4e401eb84be56bedf36108b3, nca082b3b2a4e401eb84be56bedf36108b4</t>
         </is>
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>n4f3d3308f60d48e78aa7729ed0028a2fb3, n4f3d3308f60d48e78aa7729ed0028a2fb4</t>
+          <t>nca082b3b2a4e401eb84be56bedf36108b3, nca082b3b2a4e401eb84be56bedf36108b4</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr"/>
@@ -10607,12 +10615,12 @@
       <c r="BM39" t="inlineStr"/>
       <c r="BN39" t="inlineStr">
         <is>
-          <t>n6d33c850967c40959b1027a156eb6518b3, n6d33c850967c40959b1027a156eb6518b4</t>
+          <t>n40970c4c58ef47b5afb92474f38138a6b3, n40970c4c58ef47b5afb92474f38138a6b4</t>
         </is>
       </c>
       <c r="BO39" t="inlineStr">
         <is>
-          <t>n6d33c850967c40959b1027a156eb6518b3, n6d33c850967c40959b1027a156eb6518b4</t>
+          <t>n40970c4c58ef47b5afb92474f38138a6b3, n40970c4c58ef47b5afb92474f38138a6b4</t>
         </is>
       </c>
       <c r="BP39" t="inlineStr"/>
@@ -10896,12 +10904,12 @@
       <c r="BM40" t="inlineStr"/>
       <c r="BN40" t="inlineStr">
         <is>
-          <t>ne9ed3b9aecaf4ed08aa5ba1afeca9404b1</t>
+          <t>n385d58e316724bf8bfc0822536fd9769b1</t>
         </is>
       </c>
       <c r="BO40" t="inlineStr">
         <is>
-          <t>ne9ed3b9aecaf4ed08aa5ba1afeca9404b1</t>
+          <t>n385d58e316724bf8bfc0822536fd9769b1</t>
         </is>
       </c>
       <c r="BP40" t="inlineStr"/>
@@ -11177,22 +11185,22 @@
       <c r="BM41" t="inlineStr"/>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>n2df3c4579f3d402b99b607e66b2ddad1b1</t>
+          <t>nabd7b40594274f8fa647dfe713a48eaeb1</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>n2df3c4579f3d402b99b607e66b2ddad1b1</t>
+          <t>nabd7b40594274f8fa647dfe713a48eaeb1</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>n2df3c4579f3d402b99b607e66b2ddad1b3</t>
+          <t>nabd7b40594274f8fa647dfe713a48eaeb3</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>n2df3c4579f3d402b99b607e66b2ddad1b3</t>
+          <t>nabd7b40594274f8fa647dfe713a48eaeb3</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
@@ -16278,12 +16286,12 @@
       </c>
       <c r="BN60" t="inlineStr">
         <is>
-          <t>na5a8b9ed6406407a9dca26b809994123b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
+          <t>n473d206037a24fb8b144c97a9f119d93b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
         </is>
       </c>
       <c r="BO60" t="inlineStr">
         <is>
-          <t>na5a8b9ed6406407a9dca26b809994123b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
+          <t>n473d206037a24fb8b144c97a9f119d93b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
         </is>
       </c>
       <c r="BP60" t="inlineStr"/>
@@ -20867,12 +20875,12 @@
       </c>
       <c r="BP78" t="inlineStr">
         <is>
-          <t>nc65800fa3f144939994cc46e61376703b1</t>
+          <t>n189b8926b4ba49ea8f359a264ca0090db1</t>
         </is>
       </c>
       <c r="BQ78" t="inlineStr">
         <is>
-          <t>nc65800fa3f144939994cc46e61376703b1</t>
+          <t>n189b8926b4ba49ea8f359a264ca0090db1</t>
         </is>
       </c>
       <c r="BR78" t="inlineStr">
@@ -22161,22 +22169,22 @@
       <c r="BM83" t="inlineStr"/>
       <c r="BN83" t="inlineStr">
         <is>
-          <t>nd9eb571ee4414d3ea9587e9a1ef9f7c9b1</t>
+          <t>n719fb6e75be843b6b442662d72ffc7a7b1</t>
         </is>
       </c>
       <c r="BO83" t="inlineStr">
         <is>
-          <t>nd9eb571ee4414d3ea9587e9a1ef9f7c9b1</t>
+          <t>n719fb6e75be843b6b442662d72ffc7a7b1</t>
         </is>
       </c>
       <c r="BP83" t="inlineStr">
         <is>
-          <t>nd9eb571ee4414d3ea9587e9a1ef9f7c9b3</t>
+          <t>n719fb6e75be843b6b442662d72ffc7a7b3</t>
         </is>
       </c>
       <c r="BQ83" t="inlineStr">
         <is>
-          <t>nd9eb571ee4414d3ea9587e9a1ef9f7c9b3</t>
+          <t>n719fb6e75be843b6b442662d72ffc7a7b3</t>
         </is>
       </c>
       <c r="BR83" t="inlineStr">
@@ -22949,12 +22957,12 @@
       <c r="BM86" t="inlineStr"/>
       <c r="BN86" t="inlineStr">
         <is>
-          <t>n0b6d7c418c694dfa8f53bf9eb5151348b1, n0b6d7c418c694dfa8f53bf9eb5151348b2</t>
+          <t>n3ab4571434c64d8cb3467a5f242dc0c4b1, n3ab4571434c64d8cb3467a5f242dc0c4b2</t>
         </is>
       </c>
       <c r="BO86" t="inlineStr">
         <is>
-          <t>n0b6d7c418c694dfa8f53bf9eb5151348b1, n0b6d7c418c694dfa8f53bf9eb5151348b2</t>
+          <t>n3ab4571434c64d8cb3467a5f242dc0c4b1, n3ab4571434c64d8cb3467a5f242dc0c4b2</t>
         </is>
       </c>
       <c r="BP86" t="inlineStr"/>
@@ -24074,22 +24082,22 @@
       <c r="BM90" t="inlineStr"/>
       <c r="BN90" t="inlineStr">
         <is>
-          <t>n08709a39882e49a0bc6210aeb2ea7356b3, n08709a39882e49a0bc6210aeb2ea7356b5</t>
+          <t>n2e68452f92ab46509affcd652bbe7005b3, n2e68452f92ab46509affcd652bbe7005b5</t>
         </is>
       </c>
       <c r="BO90" t="inlineStr">
         <is>
-          <t>n08709a39882e49a0bc6210aeb2ea7356b3, n08709a39882e49a0bc6210aeb2ea7356b5</t>
+          <t>n2e68452f92ab46509affcd652bbe7005b3, n2e68452f92ab46509affcd652bbe7005b5</t>
         </is>
       </c>
       <c r="BP90" t="inlineStr">
         <is>
-          <t>n08709a39882e49a0bc6210aeb2ea7356b7</t>
+          <t>n2e68452f92ab46509affcd652bbe7005b7</t>
         </is>
       </c>
       <c r="BQ90" t="inlineStr">
         <is>
-          <t>n08709a39882e49a0bc6210aeb2ea7356b7</t>
+          <t>n2e68452f92ab46509affcd652bbe7005b7</t>
         </is>
       </c>
       <c r="BR90" t="inlineStr">
@@ -25063,22 +25071,22 @@
       <c r="BM94" t="inlineStr"/>
       <c r="BN94" t="inlineStr">
         <is>
-          <t>nd90612088c7d4a9e94f99d87870a61e3b3, nd90612088c7d4a9e94f99d87870a61e3b5</t>
+          <t>n9c50b06e351a4379b54de82cc3ad0bf1b3, n9c50b06e351a4379b54de82cc3ad0bf1b5</t>
         </is>
       </c>
       <c r="BO94" t="inlineStr">
         <is>
-          <t>nd90612088c7d4a9e94f99d87870a61e3b3, nd90612088c7d4a9e94f99d87870a61e3b5</t>
+          <t>n9c50b06e351a4379b54de82cc3ad0bf1b3, n9c50b06e351a4379b54de82cc3ad0bf1b5</t>
         </is>
       </c>
       <c r="BP94" t="inlineStr">
         <is>
-          <t>nd90612088c7d4a9e94f99d87870a61e3b7</t>
+          <t>n9c50b06e351a4379b54de82cc3ad0bf1b7</t>
         </is>
       </c>
       <c r="BQ94" t="inlineStr">
         <is>
-          <t>nd90612088c7d4a9e94f99d87870a61e3b7</t>
+          <t>n9c50b06e351a4379b54de82cc3ad0bf1b7</t>
         </is>
       </c>
       <c r="BR94" t="inlineStr">
@@ -25897,12 +25905,12 @@
       </c>
       <c r="BN97" t="inlineStr">
         <is>
-          <t>ndb4ebdd8bdef41d6b41faaad3c8d614cb1</t>
+          <t>n1d457ef97f4541b991e774e0ef77205ab1</t>
         </is>
       </c>
       <c r="BO97" t="inlineStr">
         <is>
-          <t>ndb4ebdd8bdef41d6b41faaad3c8d614cb1</t>
+          <t>n1d457ef97f4541b991e774e0ef77205ab1</t>
         </is>
       </c>
       <c r="BP97" t="inlineStr"/>
@@ -28791,12 +28799,12 @@
       <c r="BM109" t="inlineStr"/>
       <c r="BN109" t="inlineStr">
         <is>
-          <t>nd9ff4291497b4f738baedb5ef335fe73b1, nd9ff4291497b4f738baedb5ef335fe73b2</t>
+          <t>n0c7153e579c5459ba422335ff4d7a272b1, n0c7153e579c5459ba422335ff4d7a272b2</t>
         </is>
       </c>
       <c r="BO109" t="inlineStr">
         <is>
-          <t>nd9ff4291497b4f738baedb5ef335fe73b1, nd9ff4291497b4f738baedb5ef335fe73b2</t>
+          <t>n0c7153e579c5459ba422335ff4d7a272b1, n0c7153e579c5459ba422335ff4d7a272b2</t>
         </is>
       </c>
       <c r="BP109" t="inlineStr"/>
@@ -37867,12 +37875,12 @@
       <c r="BM142" t="inlineStr"/>
       <c r="BN142" t="inlineStr">
         <is>
-          <t>n33fcc512c49c4ff6b34babb58299cf75b1</t>
+          <t>n7f7d721c4294429fa9e60aa20d8a148eb1</t>
         </is>
       </c>
       <c r="BO142" t="inlineStr">
         <is>
-          <t>n33fcc512c49c4ff6b34babb58299cf75b1</t>
+          <t>n7f7d721c4294429fa9e60aa20d8a148eb1</t>
         </is>
       </c>
       <c r="BP142" t="inlineStr"/>
@@ -38149,12 +38157,12 @@
       <c r="BM143" t="inlineStr"/>
       <c r="BN143" t="inlineStr">
         <is>
-          <t>n32237aee44da4072b37e5cfaaf63d857b1</t>
+          <t>nf3a95ff3b0084e419923e556eef9feb4b1</t>
         </is>
       </c>
       <c r="BO143" t="inlineStr">
         <is>
-          <t>n32237aee44da4072b37e5cfaaf63d857b1</t>
+          <t>nf3a95ff3b0084e419923e556eef9feb4b1</t>
         </is>
       </c>
       <c r="BP143" t="inlineStr"/>
@@ -38702,22 +38710,22 @@
       </c>
       <c r="BN145" t="inlineStr">
         <is>
-          <t>n3370fd46a4c74366abb405c451ee2ebdb1, n3370fd46a4c74366abb405c451ee2ebdb3, n3370fd46a4c74366abb405c451ee2ebdb5, n3370fd46a4c74366abb405c451ee2ebdb7</t>
+          <t>nc381259b2c1e4a4585fe161174b68472b1, nc381259b2c1e4a4585fe161174b68472b3, nc381259b2c1e4a4585fe161174b68472b5, nc381259b2c1e4a4585fe161174b68472b7</t>
         </is>
       </c>
       <c r="BO145" t="inlineStr">
         <is>
-          <t>n3370fd46a4c74366abb405c451ee2ebdb1, n3370fd46a4c74366abb405c451ee2ebdb3, n3370fd46a4c74366abb405c451ee2ebdb5, n3370fd46a4c74366abb405c451ee2ebdb7</t>
+          <t>nc381259b2c1e4a4585fe161174b68472b1, nc381259b2c1e4a4585fe161174b68472b3, nc381259b2c1e4a4585fe161174b68472b5, nc381259b2c1e4a4585fe161174b68472b7</t>
         </is>
       </c>
       <c r="BP145" t="inlineStr">
         <is>
-          <t>n3370fd46a4c74366abb405c451ee2ebdb9</t>
+          <t>nc381259b2c1e4a4585fe161174b68472b9</t>
         </is>
       </c>
       <c r="BQ145" t="inlineStr">
         <is>
-          <t>n3370fd46a4c74366abb405c451ee2ebdb9</t>
+          <t>nc381259b2c1e4a4585fe161174b68472b9</t>
         </is>
       </c>
       <c r="BR145" t="inlineStr">
@@ -41517,6 +41525,472 @@
         <v>1</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://w3id.org/bmat</t>
+        </is>
+      </c>
+      <c r="B158" t="b">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>bmat</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>bmat</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>bmat</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>BMAT - Ontology for defining building materials.</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>BMAT - Ontology for defining building materials.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Ontology for defining building materials.
+The suggested prefix for the BMAT namespace is bmat
+It is recommended to use BMAT in conjunction with BROT for defining a bridge construction and its aggregated components.</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Ontology for defining building materials.
+The suggested prefix for the BMAT namespace is bmat
+It is recommended to use BMAT in conjunction with BROT for defining a bridge construction and its aggregated components.</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V158" t="inlineStr"/>
+      <c r="W158" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>brcomp, brot</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>schema, foaf, vann, cd</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>foaf, vann, schema, brcomp</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>foaf, vann, schema, brcomp</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="inlineStr"/>
+      <c r="AK158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN158" t="inlineStr"/>
+      <c r="AO158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>bcore, bcoremat</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>bcore, bcoremat</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AV158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr"/>
+      <c r="AX158" t="inlineStr"/>
+      <c r="AY158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ158" t="inlineStr"/>
+      <c r="BA158" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB158" t="inlineStr"/>
+      <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="inlineStr">
+        <is>
+          <t>https://alhakam.github.io/bmat/</t>
+        </is>
+      </c>
+      <c r="BF158" t="inlineStr"/>
+      <c r="BG158" t="inlineStr">
+        <is>
+          <t>https://alhakam.github.io/bmat/</t>
+        </is>
+      </c>
+      <c r="BH158" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="BI158" t="inlineStr"/>
+      <c r="BJ158" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="BK158" t="inlineStr"/>
+      <c r="BL158" t="inlineStr"/>
+      <c r="BM158" t="inlineStr"/>
+      <c r="BN158" t="inlineStr"/>
+      <c r="BO158" t="inlineStr"/>
+      <c r="BP158" t="inlineStr"/>
+      <c r="BQ158" t="inlineStr"/>
+      <c r="BR158" t="inlineStr">
+        <is>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {brot: https://w3id.org/brot#}, {foaf: http://xmlns.com/foaf/0.1/}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {vann: http://purl.org/vocab/vann/}, {schema: http://schema.org/#}, {brcomp: https://w3id.org/brcomp#}, {None: http://purl.org/dc/}</t>
+        </is>
+      </c>
+      <c r="BS158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU158" t="n">
+        <v>26</v>
+      </c>
+      <c r="BV158" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX158" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY158" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ158" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA158" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB158" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC158" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD158" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://w3id.org//brcomp#</t>
+        </is>
+      </c>
+      <c r="B159" t="b">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>brcomp</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>brcomp</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>brcomp</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Bridge Components (BRCOMP)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Bridge Components (BRCOMP)</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>he ontology for Bridge Components (BRCOMP) allows the further classification of Bridge Elements defined in BROT. Furthermore, additional domain-specific data properties can be assigned to the instances of Bridge Element.
+The namespace for BRCOMP terms is https://w3id.org//brcomp#
+The suggested prefix for the BRCOMP namespace is brcomp
+It is recommended to use BRCOMP in conjunction with BROT for defining a bridge construction and its aggregated components.</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>he ontology for Bridge Components (BRCOMP) allows the further classification of Bridge Elements defined in BROT. Furthermore, additional domain-specific data properties can be assigned to the instances of Bridge Element.
+The namespace for BRCOMP terms is https://w3id.org//brcomp#
+The suggested prefix for the BRCOMP namespace is brcomp
+It is recommended to use BRCOMP in conjunction with BROT for defining a bridge construction and its aggregated components.</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V159" t="inlineStr"/>
+      <c r="W159" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>brot</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>vann, foaf, dc</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>foaf, vann</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>foaf, vann</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="inlineStr"/>
+      <c r="AK159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AN159" t="inlineStr"/>
+      <c r="AO159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ159" t="inlineStr"/>
+      <c r="AR159" t="inlineStr"/>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AV159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr"/>
+      <c r="AX159" t="inlineStr"/>
+      <c r="AY159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ159" t="inlineStr"/>
+      <c r="BA159" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB159" t="inlineStr"/>
+      <c r="BC159" t="inlineStr"/>
+      <c r="BD159" t="inlineStr"/>
+      <c r="BE159" t="inlineStr">
+        <is>
+          <t>https://alhakam.github.io/brcomp/</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr"/>
+      <c r="BG159" t="inlineStr">
+        <is>
+          <t>https://alhakam.github.io/brcomp/</t>
+        </is>
+      </c>
+      <c r="BH159" t="inlineStr">
+        <is>
+          <t>BE Product (Infrastructure)</t>
+        </is>
+      </c>
+      <c r="BI159" t="inlineStr"/>
+      <c r="BJ159" t="inlineStr">
+        <is>
+          <t>BE Product (Infrastructure)</t>
+        </is>
+      </c>
+      <c r="BK159" t="inlineStr"/>
+      <c r="BL159" t="inlineStr"/>
+      <c r="BM159" t="inlineStr"/>
+      <c r="BN159" t="inlineStr"/>
+      <c r="BO159" t="inlineStr"/>
+      <c r="BP159" t="inlineStr"/>
+      <c r="BQ159" t="inlineStr"/>
+      <c r="BR159" t="inlineStr">
+        <is>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {brot: https://w3id.org/brot#}, {foaf: http://xmlns.com/foaf/0.1/}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {vann: http://purl.org/vocab/vann/}, {None: http://purl.org/dc/}</t>
+        </is>
+      </c>
+      <c r="BS159" t="n">
+        <v>62</v>
+      </c>
+      <c r="BT159" t="n">
+        <v>62</v>
+      </c>
+      <c r="BU159" t="n">
+        <v>14</v>
+      </c>
+      <c r="BV159" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY159" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ159" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA159" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB159" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC159" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD159" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF159" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH159" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
